--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED13.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED13.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119W</t>
+          <t>192W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L5"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0160</t>
+          <t>SIM_XA_FIXED-4-0114</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28W</t>
+          <t>42W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,19 +1728,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第4年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>5季</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>4季</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2季</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1748,62 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年1季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-3-0082</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>97W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第3年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G56"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2141,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2098,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2141,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2215,14 +2160,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2231,7 +2176,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2241,23 +2186,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-5f01adcb6c", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2267,23 +2212,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
         </is>
       </c>
     </row>
@@ -2293,14 +2238,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2254,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2264,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2345,23 +2290,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="E22" t="n">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2371,23 +2316,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2342,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0160", "receivable_term_quarters": 2, "revenue_wan": 28.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2368,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2394,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-51a557548f", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2420,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E27" t="n">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2446,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2472,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>-8</v>
       </c>
       <c r="E30" t="n">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-98ec45924c"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2586,11 +2531,11 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2609,19 +2554,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-36</v>
+        <v>-12</v>
       </c>
       <c r="E32" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2580,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="E33" t="n">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-5aefb75402", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-26ad80580c", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2664,11 +2609,11 @@
         <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2683,23 +2628,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E35" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2654,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0114", "receivable_term_quarters": 4, "revenue_wan": 42.0}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2680,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E37" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2706,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E38" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-73dac0d3a7", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2794,11 +2739,11 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2813,23 +2758,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E40" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0082", "receivable_term_quarters": 3, "revenue_wan": 97.0}</t>
+          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
         </is>
       </c>
     </row>
@@ -2839,23 +2784,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2865,23 +2810,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-26ad80580c", "line_id": "L-353bc0007c", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2836,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E43" t="n">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2924,11 +2869,11 @@
         <v>-14</v>
       </c>
       <c r="E44" t="n">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2950,11 +2895,11 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2969,23 +2914,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>97</v>
+        <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-d97862e84d"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2995,23 +2940,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-15</v>
+        <v>42</v>
       </c>
       <c r="E47" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
+          <t>receivable_collected | {"receivable_id": "AR-12fac3de8a"}</t>
         </is>
       </c>
     </row>
@@ -3021,23 +2966,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
         </is>
       </c>
     </row>
@@ -3054,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3073,177 +3018,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E51" t="n">
-        <v>162</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E52" t="n">
-        <v>148</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E53" t="n">
-        <v>134</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E54" t="n">
-        <v>119</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-353bc0007c"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>119</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-353bc0007c", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>53</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>119</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-353bc0007c", "asset_type": "production_line"}</t>
         </is>
@@ -3350,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3575,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -3640,10 +3429,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3665,10 +3454,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>20</v>
-      </c>
-      <c r="G17" t="n">
-        <v>80</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3690,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3712,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -3737,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-79</v>
       </c>
       <c r="F20" t="n">
-        <v>-75</v>
+        <v>-79</v>
       </c>
       <c r="G20" t="n">
-        <v>-66</v>
+        <v>-57</v>
       </c>
       <c r="H20" t="n">
-        <v>-69</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="21">
@@ -3787,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-81.2</v>
+        <v>-72.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-84.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="23">
@@ -3837,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-81.2</v>
+        <v>-72.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-84.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="25">
@@ -3887,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-81.2</v>
+        <v>-72.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-84.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="28">
@@ -3986,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="F30" t="n">
-        <v>254</v>
+        <v>334</v>
       </c>
       <c r="G30" t="n">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="H30" t="n">
-        <v>119</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
@@ -4017,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4039,10 +3828,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4061,16 +3850,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>20</v>
-      </c>
-      <c r="F33" t="n">
-        <v>20</v>
-      </c>
-      <c r="G33" t="n">
-        <v>80</v>
-      </c>
-      <c r="H33" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -4111,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F35" t="n">
         <v>334</v>
       </c>
       <c r="G35" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="H35" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
@@ -4236,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F40" t="n">
         <v>400.4</v>
       </c>
       <c r="G40" t="n">
-        <v>319.2</v>
+        <v>328.2</v>
       </c>
       <c r="H40" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41">
@@ -4414,13 +4203,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-184.4</v>
+        <v>-180.4</v>
       </c>
       <c r="G47" t="n">
         <v>-274.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-355.8</v>
+        <v>-346.8</v>
       </c>
     </row>
     <row r="48">
@@ -4436,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-81.2</v>
+        <v>-72.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-84.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="49">
@@ -4461,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F49" t="n">
         <v>400.4</v>
       </c>
       <c r="G49" t="n">
-        <v>319.2</v>
+        <v>328.2</v>
       </c>
       <c r="H49" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50">
@@ -4486,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F50" t="n">
         <v>400.4</v>
       </c>
       <c r="G50" t="n">
-        <v>319.2</v>
+        <v>328.2</v>
       </c>
       <c r="H50" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -4566,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4715,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4864,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5013,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5162,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
